--- a/direct_ryazan_v3.xlsx
+++ b/direct_ryazan_v3.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Монтаж от 1000 ₽/м². Фикс. цена</t>
+          <t>Монтаж от 1000₽/м². Фикс. цена</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Скидка 30%. Звоните: +7 920 431 23 23</t>
+          <t>Скидка 30%. Звоните сейчас!</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Профнастил на крышу в Рязани!</t>
+          <t>Профнастил на крышу Рязань!</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
@@ -2553,7 +2553,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Скидка 30%! Звоните: +7 920 431 23 23</t>
+          <t>Скидка 30%! Звоните сейчас!</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Скидка 30%. Звоните: +7 920 431 23 23</t>
+          <t>Скидка 30%. Звоните сейчас!</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Наплавляемая кровля в Рязани!</t>
+          <t>Наплавляемая кровля Рязань!</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3273,7 +3273,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Скидка 30%. Звоните: +7 920 431 23 23</t>
+          <t>Скидка 30%. Звоните сейчас!</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y59" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Гидроизоляция кровли в Рязани!</t>
+          <t>Гидроизоляция кровли Рязань!</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Гидроизоляция крыши в Рязани</t>
+          <t>Гидроизоляция крыши Рязань</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>-своими+руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
+          <t>-своими руками -видео -инструкция -бесплатно -схема -чертеж -расчет -материалы -купить -магазин -работа -вакансия -резюме -обучение -курсы -бу -продаю -продам -форум -diy -нормы -гост</t>
         </is>
       </c>
       <c r="Y66" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Выезд сегодня: +7 920 431 23 23</t>
+          <t>Выезд сегодня! Звоните</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Срочный ремонт крыши в Рязани</t>
+          <t>Срочный ремонт в Рязань</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
